--- a/healthcare_forms/008_negative_test_result_submission--healthcare_forms.xlsx
+++ b/healthcare_forms/008_negative_test_result_submission--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -630,7 +630,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>12 hour format (ex. 12:00 PM)</t>
+          <t>12 hour format (ex. 12 -00 PM)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Test Result</t>
+          <t>Test Result File</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -774,12 +774,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>submit_form</t>
+          <t>submit_form_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Submit Form</t>
+          <t>Submit Form 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -797,12 +797,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>contact_details</t>
+          <t>contact_details_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Contact Details</t>
+          <t>Contact Details 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -827,8 +827,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -856,12 +856,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'pcr'}</t>
+          <t>pcr</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'PCR'}</t>
+          <t>PCR</t>
         </is>
       </c>
     </row>
@@ -873,12 +873,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'rapid_antigen'}</t>
+          <t>rapid_antigen</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Rapid Antigen'}</t>
+          <t>Rapid Antigen</t>
         </is>
       </c>
     </row>
@@ -890,12 +890,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'rapid_antibody'}</t>
+          <t>rapid_antibody</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Rapid Antibody'}</t>
+          <t>Rapid Antibody</t>
         </is>
       </c>
     </row>
@@ -907,12 +907,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -924,12 +924,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'lab_results'}</t>
+          <t>lab_results</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Lab Results'}</t>
+          <t>Lab Results</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'positive_test_results'}</t>
+          <t>positive_test_results</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Positive Test Results'}</t>
+          <t>Positive Test Results</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'negative_test_results'}</t>
+          <t>negative_test_results</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Negative Test Results'}</t>
+          <t>Negative Test Results</t>
         </is>
       </c>
     </row>
